--- a/docs/oc-mensuales/suministro-de-combustibles/ene-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2364.35</v>
+        <v>2303.97</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2623.46</v>
+        <v>2556.47</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5656.33</v>
+        <v>5511.89</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>11312.66</v>
+        <v>11023.78</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>11312.66</v>
+        <v>11023.78</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6787.59</v>
+        <v>6614.27</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11312.66</v>
+        <v>11023.78</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7918.86</v>
+        <v>7716.64</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>12841</v>
+        <v>12513.09</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5656.33</v>
+        <v>5511.89</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2375.66</v>
+        <v>2314.99</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>13575.19</v>
+        <v>13228.53</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3959.43</v>
+        <v>3858.32</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5792.08</v>
+        <v>5644.17</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>35854.33</v>
+        <v>34938.76</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5656.33</v>
+        <v>5511.89</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>8819.02</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3959.43</v>
+        <v>3858.32</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6787.59</v>
+        <v>6614.27</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4525.06</v>
+        <v>4436.8</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5090.7</v>
+        <v>4991.4</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>8873.610000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>33655.15</v>
+        <v>32998.72</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2375.66</v>
+        <v>2329.32</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4164.13</v>
+        <v>4082.91</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6900.72</v>
+        <v>6766.13</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>26019.11</v>
+        <v>25511.62</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>25286.05</v>
+        <v>24792.86</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3739.04</v>
+        <v>3666.12</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5656.33</v>
+        <v>5546</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>40725.56</v>
+        <v>39931.23</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2488.78</v>
+        <v>2440.24</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2375.66</v>
+        <v>2329.32</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8833.33</v>
+        <v>8661.040000000001</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4371.61</v>
+        <v>4286.34</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>8484.49</v>
+        <v>8319.01</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4525.06</v>
+        <v>4436.8</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>22625.31</v>
+        <v>22184.02</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4525.06</v>
+        <v>4436.8</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19370.79</v>
+        <v>18992.97</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>37331.77</v>
+        <v>36603.63</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2828.16</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>28281.64</v>
+        <v>27620.04</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>20362.78</v>
+        <v>19886.43</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3167.54</v>
+        <v>3093.44</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>8838.41</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>4038.62</v>
+        <v>3944.14</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>23756.58</v>
+        <v>23200.83</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>20362.78</v>
+        <v>19886.43</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4298.81</v>
+        <v>4198.25</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>8838.41</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2828.16</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12202.96</v>
+        <v>11917.49</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4130.35</v>
+        <v>4033.73</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>11312.66</v>
+        <v>11048.01</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>11312.66</v>
+        <v>11048.01</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>8328.42</v>
+        <v>8133.59</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>14706.45</v>
+        <v>14362.42</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>25340.04</v>
+        <v>24747.25</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3167.54</v>
+        <v>3093.44</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2828.16</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8484.49</v>
+        <v>8286.01</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>33937.97</v>
+        <v>33144.04</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2454.51</v>
+        <v>2397.09</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>7337.92</v>
+        <v>7166.26</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>40725.56</v>
+        <v>39772.85</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>37331.77</v>
+        <v>36458.45</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5656.33</v>
+        <v>5524.01</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7758.56</v>
+        <v>7577.06</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7918.86</v>
+        <v>7733.61</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>6787.59</v>
+        <v>6628.81</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>18269.94</v>
+        <v>18008.07</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>8031.99</v>
+        <v>7916.86</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>10181.39</v>
+        <v>10035.46</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>13575.19</v>
+        <v>13380.61</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>7480.85</v>
+        <v>7373.63</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3393.8</v>
+        <v>3345.15</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2601.91</v>
+        <v>2564.62</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>22625.31</v>
+        <v>22301.02</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>22625.31</v>
+        <v>22301.02</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>22625.31</v>
+        <v>22301.02</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>15837.72</v>
+        <v>15610.71</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>22625.31</v>
+        <v>22301.02</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>36200.5</v>
+        <v>35681.63</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>4525.06</v>
+        <v>4460.2</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3393.8</v>
+        <v>3345.15</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3393.8</v>
+        <v>3345.15</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>8920.41</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>11312.66</v>
+        <v>11150.51</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>8196.02</v>
+        <v>8078.54</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10181.39</v>
+        <v>10035.46</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>22625.31</v>
+        <v>22301.02</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2375.66</v>
+        <v>2341.61</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8823.870000000001</v>
+        <v>8697.4</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>33937.97</v>
+        <v>33451.53</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>4597.46</v>
+        <v>4531.57</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3054.42</v>
+        <v>3010.64</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2988.89</v>
+        <v>2946.05</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>11312.66</v>
+        <v>11150.51</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>11813.3</v>
+        <v>11643.98</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>11312.66</v>
+        <v>11150.51</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3393.8</v>
+        <v>3345.15</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5656.33</v>
+        <v>5575.25</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5656.33</v>
+        <v>5575.25</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6787.59</v>
+        <v>6701.44</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7918.86</v>
+        <v>7818.35</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2367.74</v>
+        <v>2337.69</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>3393.8</v>
+        <v>3350.72</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3393.8</v>
+        <v>3350.72</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2375.66</v>
+        <v>2345.5</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3393.8</v>
+        <v>3350.72</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2488.78</v>
+        <v>2457.19</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2828.16</v>
+        <v>2792.27</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>10181.39</v>
+        <v>10052.16</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2375.66</v>
+        <v>2345.5</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>5656.33</v>
+        <v>5584.53</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>8935.25</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>11312.66</v>
+        <v>11169.07</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>22625.31</v>
+        <v>22338.13</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2828.16</v>
+        <v>2792.27</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>8935.25</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2828.16</v>
+        <v>2792.27</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>12443.92</v>
+        <v>12285.97</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>5656.33</v>
+        <v>5584.53</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2367.21</v>
+        <v>2337.16</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2491.82</v>
+        <v>2460.19</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4525.06</v>
+        <v>4467.63</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3393.8</v>
+        <v>3350.72</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2828.16</v>
+        <v>2792.27</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6787.59</v>
+        <v>6701.44</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>4525.06</v>
+        <v>4467.63</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6787.59</v>
+        <v>6701.44</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>6787.59</v>
+        <v>6701.44</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2375.66</v>
+        <v>2345.5</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>11312.66</v>
+        <v>11169.07</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2386.97</v>
+        <v>2352.57</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>11312.66</v>
+        <v>11149.64</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>13009.55</v>
+        <v>12822.09</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>39028.66</v>
+        <v>38466.26</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>67875.94</v>
+        <v>66897.84</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2488.78</v>
+        <v>2452.92</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>28281.63</v>
+        <v>27874.08</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5656.33</v>
+        <v>5574.82</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>7918.86</v>
+        <v>7804.75</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2601.91</v>
+        <v>2564.42</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>11312.66</v>
+        <v>11149.64</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>18100.01</v>
+        <v>17839.19</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>37331.77</v>
+        <v>36793.81</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3393.8</v>
+        <v>3344.89</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>678759.37</v>
+        <v>668978.36</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>4185.68</v>
+        <v>4125.37</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>22625.31</v>
+        <v>22299.28</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>22625.31</v>
+        <v>22299.28</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>14706.45</v>
+        <v>14494.53</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>4525.06</v>
+        <v>4459.86</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>22489.56</v>
+        <v>22165.48</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>3167.54</v>
+        <v>3121.9</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>6187.09</v>
+        <v>6097.94</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>24050.71</v>
+        <v>23704.13</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>33937.97</v>
+        <v>33448.92</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>14892.95</v>
+        <v>14678.34</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>10703.1</v>
+        <v>10548.86</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>16968.98</v>
+        <v>16724.46</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2375.66</v>
+        <v>2341.42</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2488.78</v>
+        <v>2452.92</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>23190.95</v>
+        <v>22891.22</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>4525.06</v>
+        <v>4466.58</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>38462.99</v>
+        <v>37965.88</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>11312.66</v>
+        <v>11166.45</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4748.6</v>
+        <v>4687.22</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3620.05</v>
+        <v>3573.26</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>16968.98</v>
+        <v>16749.67</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>5769.45</v>
+        <v>5694.89</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>4977.57</v>
+        <v>4913.24</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3393.8</v>
+        <v>3349.93</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3488.39</v>
+        <v>3443.31</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>6787.59</v>
+        <v>6699.87</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>3679.39</v>
+        <v>3631.84</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>18100.25</v>
+        <v>17866.32</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8077.24</v>
+        <v>7972.84</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2692.41</v>
+        <v>2657.61</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>56563.28</v>
+        <v>55832.24</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>38463.03</v>
+        <v>37965.92</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>3392.63</v>
+        <v>3348.78</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>38463.03</v>
+        <v>37965.92</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>33937.97</v>
+        <v>33499.34</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>5654.34</v>
+        <v>5581.26</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>5223.27</v>
+        <v>5155.76</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3959.43</v>
+        <v>3908.26</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>12443.92</v>
+        <v>12419.41</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2375.66</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>19231.52</v>
+        <v>19193.64</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>5854.3</v>
+        <v>5842.77</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>4525.06</v>
+        <v>4516.15</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3846.3</v>
+        <v>3838.73</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>14706.45</v>
+        <v>14677.49</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2375.66</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>11312.66</v>
+        <v>11290.38</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>16968.98</v>
+        <v>16935.57</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>33937.97</v>
+        <v>33871.13</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>8196.02</v>
+        <v>8179.88</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>28621.02</v>
+        <v>28564.65</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9032.299999999999</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>13575.19</v>
+        <v>13548.45</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3393.8</v>
+        <v>3387.11</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2375.66</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2375.66</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>5656.33</v>
+        <v>5645.19</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2375.66</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7890.69</v>
+        <v>7875.15</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>4525.06</v>
+        <v>4516.15</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3054.42</v>
+        <v>3048.4</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>64919.94</v>
+        <v>64792.09</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>9944.389999999999</v>
+        <v>9924.809999999999</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2375.66</v>
+        <v>2370.98</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>4150.36</v>
+        <v>4142.18</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>4849.66</v>
+        <v>4849.69</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>4185.68</v>
+        <v>4185.71</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9050.18</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3393.8</v>
+        <v>3393.82</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>6787.59</v>
+        <v>6787.64</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>6787.59</v>
+        <v>6787.64</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>4807.88</v>
+        <v>4807.91</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>7918.86</v>
+        <v>7918.91</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>5769.45</v>
+        <v>5769.49</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>2375.66</v>
+        <v>2375.67</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>11312.66</v>
+        <v>11312.73</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2375.66</v>
+        <v>2375.67</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>78906.91</v>
+        <v>78907.42</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>6787.59</v>
+        <v>6787.64</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>3393.8</v>
+        <v>3393.82</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2601.91</v>
+        <v>2601.93</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3959.43</v>
+        <v>3959.46</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>33768.28</v>
+        <v>33768.5</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>5656.33</v>
+        <v>5656.36</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>54809.82</v>
+        <v>54810.17</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>13801.44</v>
+        <v>13801.53</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>7353.23</v>
+        <v>7353.27</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>3506.92</v>
+        <v>3506.95</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>25453.48</v>
+        <v>25453.64</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>13575.19</v>
+        <v>13575.27</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>13575.19</v>
+        <v>13575.27</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3393.8</v>
+        <v>3393.82</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>11312.66</v>
+        <v>11312.73</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>11312.66</v>
+        <v>11312.73</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>7918.86</v>
+        <v>7918.91</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>5656.33</v>
+        <v>5656.36</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>5656.33</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>16968.98</v>
+        <v>16992.55</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2488.78</v>
+        <v>2492.24</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>5656.33</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>5656.33</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>4525.06</v>
+        <v>4531.35</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>11189.35</v>
+        <v>11204.88</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>7918.86</v>
+        <v>7929.85</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>6787.59</v>
+        <v>6797.02</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>7918.86</v>
+        <v>7929.85</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>20362.78</v>
+        <v>20391.06</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>22625.31</v>
+        <v>22656.73</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3393.8</v>
+        <v>3398.51</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>11312.66</v>
+        <v>11328.36</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>45250.62</v>
+        <v>45313.46</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2828.16</v>
+        <v>2832.09</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>30544.17</v>
+        <v>30586.58</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5656.33</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>5215.7</v>
+        <v>5222.94</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>5656.33</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>7918.86</v>
+        <v>7929.85</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2367.21</v>
+        <v>2370.49</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>28281.64</v>
+        <v>28320.91</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>26149.2</v>
+        <v>26185.51</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>16968.98</v>
+        <v>16992.55</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>23567.66</v>
+        <v>23600.38</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3393.8</v>
+        <v>3398.51</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>16968.98</v>
+        <v>16992.55</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>22625.31</v>
+        <v>22656.73</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>16968.98</v>
+        <v>16992.55</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>22625.31</v>
+        <v>22609.86</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3564.08</v>
+        <v>3561.65</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3393.8</v>
+        <v>3391.48</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>33937.97</v>
+        <v>33914.78</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2828.16</v>
+        <v>2826.23</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>52603.85</v>
+        <v>52567.91</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>3444.05</v>
+        <v>3441.7</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>33937.97</v>
+        <v>33914.78</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>11312.66</v>
+        <v>11304.93</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>4525.06</v>
+        <v>4521.97</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>33937.97</v>
+        <v>33914.78</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>12443.92</v>
+        <v>12435.42</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2375.66</v>
+        <v>2374.03</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>16968.98</v>
+        <v>16957.39</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>22625.31</v>
+        <v>22609.86</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>10181.39</v>
+        <v>10174.44</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>14706.45</v>
+        <v>14696.41</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>13575.19</v>
+        <v>13565.91</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>6335.09</v>
+        <v>6330.76</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>3393.8</v>
+        <v>3391.48</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>27621.59</v>
+        <v>27602.72</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2828.16</v>
+        <v>2826.23</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>8597.620000000001</v>
+        <v>8591.75</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2828.16</v>
+        <v>2826.23</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2488.78</v>
+        <v>2487.08</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>4704.79</v>
+        <v>4701.57</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>9615.76</v>
+        <v>9609.190000000001</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>3393.8</v>
+        <v>3391.48</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>3393.8</v>
+        <v>3391.48</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2367.21</v>
+        <v>2365.59</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>18665.88</v>
+        <v>18653.13</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2828.16</v>
+        <v>2826.23</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>20362.78</v>
+        <v>20348.87</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>33937.97</v>
+        <v>33914.78</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>33937.97</v>
+        <v>33914.78</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>11312.66</v>
+        <v>11304.93</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>6787.59</v>
+        <v>6782.96</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>22625.31</v>
+        <v>22609.86</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2375.66</v>
+        <v>2374.03</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2375.66</v>
+        <v>2374.03</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>11313.77</v>
+        <v>11306.05</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>3393.8</v>
+        <v>3391.48</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2375.66</v>
+        <v>2374.03</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>3393.8</v>
+        <v>3391.48</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>3453.8</v>
+        <v>3451.44</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>27829.13</v>
+        <v>27810.12</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>10294.52</v>
+        <v>10287.48</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>5656.33</v>
+        <v>5652.46</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>3167.54</v>
+        <v>3165.38</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2601.91</v>
+        <v>2600.13</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>11312.66</v>
+        <v>11304.93</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>22625.31</v>
+        <v>22547.66</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>15097.84</v>
+        <v>15046.03</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3129.12</v>
+        <v>3118.38</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>28281.64</v>
+        <v>28184.58</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>5656.33</v>
+        <v>5636.92</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>11312.66</v>
+        <v>11273.83</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>38463.03</v>
+        <v>38331.02</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>4525.06</v>
+        <v>4509.53</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>13956.74</v>
+        <v>13908.84</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>3620.05</v>
+        <v>3607.63</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2757.74</v>
+        <v>2748.28</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>16968.98</v>
+        <v>16910.75</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>8935.57</v>
+        <v>8904.9</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>3393.8</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>3393.8</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>15837.72</v>
+        <v>15783.36</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>5656.33</v>
+        <v>5636.92</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>3393.8</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>3393.8</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>11312.66</v>
+        <v>11273.83</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>11312.66</v>
+        <v>11273.83</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>11312.66</v>
+        <v>11273.83</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>113126.56</v>
+        <v>112738.3</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>4242.25</v>
+        <v>4227.69</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>6108.83</v>
+        <v>6087.87</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>2639.24</v>
+        <v>2630.18</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>289264.62</v>
+        <v>288271.83</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2367.21</v>
+        <v>2359.08</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>2375.66</v>
+        <v>2367.5</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>4525.06</v>
+        <v>4509.53</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>45250.62</v>
+        <v>45095.32</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>45250.62</v>
+        <v>45095.32</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>5656.33</v>
+        <v>5636.92</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2367.21</v>
+        <v>2359.08</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>18665.88</v>
+        <v>18601.82</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>3384.33</v>
+        <v>3372.71</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>15837.72</v>
+        <v>15783.36</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>12217.67</v>
+        <v>12175.74</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>8576.870000000001</v>
+        <v>8547.43</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>39594.3</v>
+        <v>39458.41</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>5178.5</v>
+        <v>5160.72</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>5718.55</v>
+        <v>5698.92</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2488.78</v>
+        <v>2480.24</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>3393.8</v>
+        <v>3382.15</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2988.68</v>
+        <v>2978.42</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>8484.49</v>
+        <v>8455.370000000001</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>70658.85000000001</v>
+        <v>70416.34</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>33937.97</v>
+        <v>33821.49</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2601.91</v>
+        <v>2592.98</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2488.78</v>
+        <v>2475.64</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>3393.8</v>
+        <v>3375.87</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>4525.06</v>
+        <v>4501.16</v>
       </c>
     </row>
     <row r="406">
@@ -25221,7 +25221,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>444433.68</v>
+        <v>442085.98</v>
       </c>
     </row>
     <row r="407">
@@ -25282,7 +25282,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>22625.31</v>
+        <v>22505.8</v>
       </c>
     </row>
     <row r="408">
@@ -25343,7 +25343,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>47513.16</v>
+        <v>47262.17</v>
       </c>
     </row>
     <row r="409">
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>75794.8</v>
+        <v>75394.41</v>
       </c>
     </row>
     <row r="410">
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2375.66</v>
+        <v>2363.11</v>
       </c>
     </row>
     <row r="411">
@@ -25526,7 +25526,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>2955.64</v>
+        <v>2940.03</v>
       </c>
     </row>
     <row r="412">
@@ -25587,7 +25587,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>8060.27</v>
+        <v>8017.69</v>
       </c>
     </row>
     <row r="413">
@@ -25648,7 +25648,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>6565.41</v>
+        <v>6530.73</v>
       </c>
     </row>
     <row r="414">
@@ -25709,7 +25709,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>5090.7</v>
+        <v>5063.8</v>
       </c>
     </row>
     <row r="415">
@@ -25770,7 +25770,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>12614.7</v>
+        <v>12548.07</v>
       </c>
     </row>
     <row r="416">
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>18378.26</v>
+        <v>18281.18</v>
       </c>
     </row>
     <row r="417">
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>22625.31</v>
+        <v>22505.8</v>
       </c>
     </row>
     <row r="418">
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9002.32</v>
       </c>
     </row>
     <row r="419">
@@ -26014,7 +26014,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4525.06</v>
+        <v>4501.16</v>
       </c>
     </row>
     <row r="420">
@@ -26075,7 +26075,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>11312.66</v>
+        <v>11252.9</v>
       </c>
     </row>
     <row r="421">
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>11312.66</v>
+        <v>11252.9</v>
       </c>
     </row>
     <row r="422">
@@ -26197,7 +26197,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>2375.66</v>
+        <v>2363.11</v>
       </c>
     </row>
     <row r="423">
@@ -26258,7 +26258,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>16968.98</v>
+        <v>16879.35</v>
       </c>
     </row>
     <row r="424">
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>73532.25999999999</v>
+        <v>73143.83</v>
       </c>
     </row>
     <row r="425">
@@ -26380,7 +26380,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>4525.06</v>
+        <v>4501.16</v>
       </c>
     </row>
     <row r="426">
@@ -26441,7 +26441,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>14140.82</v>
+        <v>14066.12</v>
       </c>
     </row>
     <row r="427">
@@ -26502,7 +26502,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>3393.8</v>
+        <v>3375.87</v>
       </c>
     </row>
     <row r="428">
@@ -26563,7 +26563,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>3393.8</v>
+        <v>3375.87</v>
       </c>
     </row>
     <row r="429">
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>2375.66</v>
+        <v>2363.11</v>
       </c>
     </row>
     <row r="430">
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>6787.59</v>
+        <v>6751.74</v>
       </c>
     </row>
     <row r="431">
@@ -26746,7 +26746,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>5656.33</v>
+        <v>5626.45</v>
       </c>
     </row>
     <row r="432">
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>5656.33</v>
+        <v>5626.45</v>
       </c>
     </row>
     <row r="433">
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>2367.21</v>
+        <v>2354.7</v>
       </c>
     </row>
     <row r="434">
@@ -26929,7 +26929,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>4525.06</v>
+        <v>4501.16</v>
       </c>
     </row>
     <row r="435">
@@ -26990,7 +26990,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>5826.02</v>
+        <v>5795.24</v>
       </c>
     </row>
     <row r="436">
@@ -27051,7 +27051,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>4525.06</v>
+        <v>4501.16</v>
       </c>
     </row>
     <row r="437">
@@ -27112,7 +27112,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>2367.21</v>
+        <v>2354.7</v>
       </c>
     </row>
     <row r="438">
@@ -27173,7 +27173,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>6787.59</v>
+        <v>6751.74</v>
       </c>
     </row>
     <row r="439">
@@ -27234,7 +27234,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>3393.8</v>
+        <v>3375.87</v>
       </c>
     </row>
     <row r="440">
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>5656.33</v>
+        <v>5626.45</v>
       </c>
     </row>
     <row r="441">
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>3167.54</v>
+        <v>3150.81</v>
       </c>
     </row>
     <row r="442">
@@ -27417,7 +27417,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>6787.59</v>
+        <v>6751.74</v>
       </c>
     </row>
     <row r="443">
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>33937.97</v>
+        <v>33758.69</v>
       </c>
     </row>
     <row r="444">
@@ -27539,7 +27539,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>7890.69</v>
+        <v>7849.01</v>
       </c>
     </row>
     <row r="445">
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>3507.13</v>
+        <v>3488.61</v>
       </c>
     </row>
     <row r="446">
@@ -27661,7 +27661,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>2601.91</v>
+        <v>2588.17</v>
       </c>
     </row>
     <row r="447">
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>6787.59</v>
+        <v>6751.74</v>
       </c>
     </row>
     <row r="448">
@@ -27783,7 +27783,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>2375.66</v>
+        <v>2363.11</v>
       </c>
     </row>
     <row r="449">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>37331.77</v>
+        <v>37134.56</v>
       </c>
     </row>
     <row r="450">
@@ -27905,7 +27905,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>4525.06</v>
+        <v>4501.16</v>
       </c>
     </row>
     <row r="451">
@@ -27966,7 +27966,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>3393.8</v>
+        <v>3375.87</v>
       </c>
     </row>
     <row r="452">
@@ -28027,7 +28027,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>3959.43</v>
+        <v>3938.51</v>
       </c>
     </row>
     <row r="453">
@@ -28088,7 +28088,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>27150.37</v>
+        <v>27006.95</v>
       </c>
     </row>
     <row r="454">
@@ -28149,7 +28149,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>3393.8</v>
+        <v>3372.53</v>
       </c>
     </row>
     <row r="455">
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2375.66</v>
+        <v>2360.77</v>
       </c>
     </row>
     <row r="456">
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>10181.39</v>
+        <v>10117.59</v>
       </c>
     </row>
     <row r="457">
@@ -28332,7 +28332,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>33937.97</v>
+        <v>33725.3</v>
       </c>
     </row>
     <row r="458">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>8993.559999999999</v>
+        <v>8937.200000000001</v>
       </c>
     </row>
     <row r="459">
@@ -28454,7 +28454,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>2715.04</v>
+        <v>2698.02</v>
       </c>
     </row>
     <row r="460">
@@ -28515,7 +28515,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>2375.66</v>
+        <v>2360.77</v>
       </c>
     </row>
     <row r="461">
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>2828.16</v>
+        <v>2810.44</v>
       </c>
     </row>
     <row r="462">
@@ -28637,7 +28637,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>3499</v>
+        <v>3477.08</v>
       </c>
     </row>
     <row r="463">
@@ -28698,7 +28698,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>22625.31</v>
+        <v>22483.53</v>
       </c>
     </row>
     <row r="464">
@@ -28759,7 +28759,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>22625.31</v>
+        <v>22483.53</v>
       </c>
     </row>
     <row r="465">
@@ -28820,7 +28820,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>22625.31</v>
+        <v>22483.53</v>
       </c>
     </row>
     <row r="466">
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>3393.8</v>
+        <v>3372.53</v>
       </c>
     </row>
     <row r="467">
@@ -28942,7 +28942,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>11312.66</v>
+        <v>11241.77</v>
       </c>
     </row>
     <row r="468">
@@ -29003,7 +29003,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>15837.72</v>
+        <v>15738.47</v>
       </c>
     </row>
     <row r="469">
@@ -29064,7 +29064,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2488.78</v>
+        <v>2473.19</v>
       </c>
     </row>
     <row r="470">
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>3393.8</v>
+        <v>3372.53</v>
       </c>
     </row>
     <row r="471">
@@ -29186,7 +29186,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>22625.31</v>
+        <v>22483.53</v>
       </c>
     </row>
     <row r="472">
@@ -29247,7 +29247,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>3393.8</v>
+        <v>3372.53</v>
       </c>
     </row>
     <row r="473">
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>37331.77</v>
+        <v>37097.83</v>
       </c>
     </row>
     <row r="474">
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>4638.19</v>
+        <v>4609.12</v>
       </c>
     </row>
     <row r="475">
@@ -29430,7 +29430,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>3393.8</v>
+        <v>3372.53</v>
       </c>
     </row>
     <row r="476">
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>6787.59</v>
+        <v>6745.06</v>
       </c>
     </row>
     <row r="477">
@@ -29552,7 +29552,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>33937.97</v>
+        <v>33725.3</v>
       </c>
     </row>
     <row r="478">
@@ -29613,7 +29613,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>33937.97</v>
+        <v>33725.3</v>
       </c>
     </row>
     <row r="479">
@@ -29674,7 +29674,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>113126.56</v>
+        <v>112417.65</v>
       </c>
     </row>
     <row r="480">
@@ -29735,7 +29735,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>4377.64</v>
+        <v>4350.21</v>
       </c>
     </row>
     <row r="481">
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>10181.39</v>
+        <v>10117.59</v>
       </c>
     </row>
     <row r="482">
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>7918.86</v>
+        <v>7869.24</v>
       </c>
     </row>
     <row r="483">
@@ -29918,7 +29918,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>10181.39</v>
+        <v>10117.59</v>
       </c>
     </row>
     <row r="484">
@@ -29979,7 +29979,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>11312.66</v>
+        <v>11241.77</v>
       </c>
     </row>
     <row r="485">
@@ -30040,7 +30040,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>5090.7</v>
+        <v>5058.79</v>
       </c>
     </row>
     <row r="486">
@@ -30101,7 +30101,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>13575.19</v>
+        <v>13490.12</v>
       </c>
     </row>
     <row r="487">
@@ -30162,7 +30162,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>56563.28</v>
+        <v>56208.83</v>
       </c>
     </row>
     <row r="488">
@@ -30223,7 +30223,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>2367.21</v>
+        <v>2352.37</v>
       </c>
     </row>
     <row r="489">
@@ -30284,7 +30284,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>4525.06</v>
+        <v>4496.71</v>
       </c>
     </row>
     <row r="490">
@@ -30345,7 +30345,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>3393.8</v>
+        <v>3372.53</v>
       </c>
     </row>
     <row r="491">
@@ -30406,7 +30406,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>6787.59</v>
+        <v>6745.06</v>
       </c>
     </row>
     <row r="492">
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2828.16</v>
+        <v>2810.44</v>
       </c>
     </row>
     <row r="493">
@@ -30528,7 +30528,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>2828.16</v>
+        <v>2810.44</v>
       </c>
     </row>
     <row r="494">
@@ -30589,7 +30589,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>3393.8</v>
+        <v>3416.04</v>
       </c>
     </row>
     <row r="495">
@@ -30650,7 +30650,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>2375.66</v>
+        <v>2391.23</v>
       </c>
     </row>
     <row r="496">
@@ -30711,7 +30711,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>2375.66</v>
+        <v>2391.23</v>
       </c>
     </row>
     <row r="497">
@@ -30772,7 +30772,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>10181.39</v>
+        <v>10248.12</v>
       </c>
     </row>
     <row r="498">
@@ -30833,7 +30833,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>2601.91</v>
+        <v>2618.96</v>
       </c>
     </row>
     <row r="499">
@@ -30894,7 +30894,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2941.29</v>
+        <v>2960.57</v>
       </c>
     </row>
     <row r="500">
@@ -30955,7 +30955,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>3167.54</v>
+        <v>3188.3</v>
       </c>
     </row>
     <row r="501">
@@ -31016,7 +31016,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>6787.59</v>
+        <v>6832.08</v>
       </c>
     </row>
     <row r="502">
@@ -31077,7 +31077,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>3393.8</v>
+        <v>3416.04</v>
       </c>
     </row>
     <row r="503">
@@ -31138,7 +31138,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>2828.16</v>
+        <v>2846.7</v>
       </c>
     </row>
     <row r="504">
@@ -31199,7 +31199,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>2375.66</v>
+        <v>2391.23</v>
       </c>
     </row>
     <row r="505">
@@ -31260,7 +31260,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>3959.43</v>
+        <v>3985.38</v>
       </c>
     </row>
     <row r="506">
@@ -31321,7 +31321,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>2367.74</v>
+        <v>2383.26</v>
       </c>
     </row>
     <row r="507">
@@ -31382,7 +31382,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2375.66</v>
+        <v>2391.23</v>
       </c>
     </row>
     <row r="508">
@@ -31443,7 +31443,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>6787.59</v>
+        <v>6832.08</v>
       </c>
     </row>
     <row r="509">
@@ -31504,7 +31504,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>6787.59</v>
+        <v>6832.08</v>
       </c>
     </row>
     <row r="510">
@@ -31565,7 +31565,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>5656.33</v>
+        <v>5693.4</v>
       </c>
     </row>
     <row r="511">
@@ -31626,7 +31626,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>23756.58</v>
+        <v>23912.28</v>
       </c>
     </row>
     <row r="512">
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>38463.03</v>
+        <v>38715.11</v>
       </c>
     </row>
     <row r="513">
@@ -31748,7 +31748,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>16968.98</v>
+        <v>17080.2</v>
       </c>
     </row>
     <row r="514">
@@ -31809,7 +31809,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>2375.66</v>
+        <v>2391.23</v>
       </c>
     </row>
     <row r="515">
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>5939.14</v>
+        <v>5978.07</v>
       </c>
     </row>
     <row r="516">
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>2370</v>
+        <v>2385.53</v>
       </c>
     </row>
     <row r="517">
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="518">
@@ -32053,7 +32053,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="519">
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>4525.06</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="520">
@@ -32175,7 +32175,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>5656.33</v>
+        <v>5732.5</v>
       </c>
     </row>
     <row r="521">
@@ -32236,7 +32236,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>3393.8</v>
+        <v>3439.5</v>
       </c>
     </row>
     <row r="522">
@@ -32297,7 +32297,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>45250.62</v>
+        <v>45859.99</v>
       </c>
     </row>
     <row r="523">
@@ -32358,7 +32358,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="524">
@@ -32419,7 +32419,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>13575.19</v>
+        <v>13758</v>
       </c>
     </row>
     <row r="525">
@@ -32480,7 +32480,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="526">
@@ -32541,7 +32541,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="527">
@@ -32602,7 +32602,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>2601.91</v>
+        <v>2636.95</v>
       </c>
     </row>
     <row r="528">
@@ -32663,7 +32663,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>13575.19</v>
+        <v>13758</v>
       </c>
     </row>
     <row r="529">
@@ -32724,7 +32724,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>73532.25999999999</v>
+        <v>74522.48</v>
       </c>
     </row>
     <row r="530">
@@ -32785,7 +32785,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>33937.97</v>
+        <v>34394.99</v>
       </c>
     </row>
     <row r="531">
@@ -32846,7 +32846,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>9153.379999999999</v>
+        <v>9276.65</v>
       </c>
     </row>
     <row r="532">
@@ -32907,7 +32907,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>2488.78</v>
+        <v>2522.3</v>
       </c>
     </row>
     <row r="533">
@@ -32968,7 +32968,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="534">
@@ -33029,7 +33029,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>2367.21</v>
+        <v>2399.09</v>
       </c>
     </row>
     <row r="535">
@@ -33090,7 +33090,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>4525.06</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="536">
@@ -33151,7 +33151,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>3314.61</v>
+        <v>3359.24</v>
       </c>
     </row>
     <row r="537">
@@ -33212,7 +33212,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>16968.98</v>
+        <v>17197.5</v>
       </c>
     </row>
     <row r="538">
@@ -33273,7 +33273,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>31109.8</v>
+        <v>31528.74</v>
       </c>
     </row>
     <row r="539">
@@ -33334,7 +33334,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>2488.78</v>
+        <v>2522.3</v>
       </c>
     </row>
     <row r="540">
@@ -33395,7 +33395,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>5656.33</v>
+        <v>5732.5</v>
       </c>
     </row>
     <row r="541">
@@ -33456,7 +33456,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="542">
@@ -33517,7 +33517,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2367.74</v>
+        <v>2399.62</v>
       </c>
     </row>
     <row r="543">
@@ -33578,7 +33578,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>33937.97</v>
+        <v>34394.99</v>
       </c>
     </row>
     <row r="544">
@@ -33639,7 +33639,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>16968.98</v>
+        <v>17197.5</v>
       </c>
     </row>
     <row r="545">
@@ -33700,7 +33700,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>2367.21</v>
+        <v>2399.09</v>
       </c>
     </row>
     <row r="546">
@@ -33761,7 +33761,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>16376.2</v>
+        <v>16596.73</v>
       </c>
     </row>
     <row r="547">
@@ -33822,7 +33822,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>33937.97</v>
+        <v>34394.99</v>
       </c>
     </row>
     <row r="548">
@@ -33883,7 +33883,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>4525.06</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="549">
@@ -33944,7 +33944,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>22625.31</v>
+        <v>22929.99</v>
       </c>
     </row>
     <row r="550">
@@ -34005,7 +34005,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>6787.59</v>
+        <v>6879</v>
       </c>
     </row>
     <row r="551">
@@ -34066,7 +34066,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>3959.43</v>
+        <v>4012.75</v>
       </c>
     </row>
     <row r="552">
@@ -34127,7 +34127,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>9004.65</v>
+        <v>9125.91</v>
       </c>
     </row>
     <row r="553">
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>5656.33</v>
+        <v>5732.5</v>
       </c>
     </row>
     <row r="554">
@@ -34249,7 +34249,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>3393.8</v>
+        <v>3439.5</v>
       </c>
     </row>
     <row r="555">
@@ -34310,7 +34310,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="556">
@@ -34371,7 +34371,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>4240.43</v>
+        <v>4297.53</v>
       </c>
     </row>
     <row r="557">
@@ -34432,7 +34432,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>7918.86</v>
+        <v>8025.5</v>
       </c>
     </row>
     <row r="558">
@@ -34493,7 +34493,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>13575.19</v>
+        <v>13758</v>
       </c>
     </row>
     <row r="559">
@@ -34554,7 +34554,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>16968.98</v>
+        <v>17197.5</v>
       </c>
     </row>
     <row r="560">
@@ -34615,7 +34615,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>4525.06</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="561">
@@ -34676,7 +34676,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>5792.08</v>
+        <v>5870.08</v>
       </c>
     </row>
     <row r="562">
@@ -34737,7 +34737,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>18100.25</v>
+        <v>18344</v>
       </c>
     </row>
     <row r="563">
@@ -34798,7 +34798,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>2715.04</v>
+        <v>2756.37</v>
       </c>
     </row>
     <row r="564">
@@ -34859,7 +34859,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>2488.78</v>
+        <v>2526.67</v>
       </c>
     </row>
     <row r="565">
@@ -34920,7 +34920,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>18665.88</v>
+        <v>18950.05</v>
       </c>
     </row>
     <row r="566">
@@ -34981,7 +34981,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>2375.66</v>
+        <v>2411.82</v>
       </c>
     </row>
     <row r="567">
@@ -35042,7 +35042,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>3365.52</v>
+        <v>3416.75</v>
       </c>
     </row>
     <row r="568">
@@ -35103,7 +35103,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>5656.33</v>
+        <v>5742.44</v>
       </c>
     </row>
     <row r="569">
@@ -35164,7 +35164,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>2375.66</v>
+        <v>2411.82</v>
       </c>
     </row>
     <row r="570">
@@ -35225,7 +35225,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>5975.34</v>
+        <v>6066.31</v>
       </c>
     </row>
     <row r="571">
@@ -35286,7 +35286,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>4978.7</v>
+        <v>5054.5</v>
       </c>
     </row>
     <row r="572">
@@ -35347,7 +35347,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>33937.97</v>
+        <v>34454.64</v>
       </c>
     </row>
     <row r="573">
@@ -35408,7 +35408,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>5090.7</v>
+        <v>5168.2</v>
       </c>
     </row>
     <row r="574">
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>2828.16</v>
+        <v>2871.22</v>
       </c>
     </row>
     <row r="575">
@@ -35530,7 +35530,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>4525.06</v>
+        <v>4593.95</v>
       </c>
     </row>
     <row r="576">
@@ -35591,7 +35591,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>5656.33</v>
+        <v>5742.44</v>
       </c>
     </row>
     <row r="577">
@@ -35652,7 +35652,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>5090.7</v>
+        <v>5168.2</v>
       </c>
     </row>
     <row r="578">
@@ -35713,7 +35713,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>11312.66</v>
+        <v>11484.88</v>
       </c>
     </row>
     <row r="579">
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>11312.66</v>
+        <v>11484.88</v>
       </c>
     </row>
     <row r="580">
@@ -35835,7 +35835,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>3393.8</v>
+        <v>3445.46</v>
       </c>
     </row>
     <row r="581">
@@ -35896,7 +35896,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>4525.06</v>
+        <v>4593.95</v>
       </c>
     </row>
     <row r="582">
@@ -35957,7 +35957,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>13575.19</v>
+        <v>13781.86</v>
       </c>
     </row>
     <row r="583">
@@ -36018,7 +36018,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>2432.22</v>
+        <v>2469.25</v>
       </c>
     </row>
     <row r="584">
@@ -36079,7 +36079,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>2941.29</v>
+        <v>2986.07</v>
       </c>
     </row>
     <row r="585">
@@ -36140,7 +36140,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>11312.66</v>
+        <v>11484.88</v>
       </c>
     </row>
     <row r="586">
@@ -36201,7 +36201,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>11312.66</v>
+        <v>11484.88</v>
       </c>
     </row>
     <row r="587">
@@ -36262,7 +36262,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>2367.21</v>
+        <v>2403.25</v>
       </c>
     </row>
     <row r="588">
@@ -36323,7 +36323,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>39594.3</v>
+        <v>40197.08</v>
       </c>
     </row>
     <row r="589">
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>3393.8</v>
+        <v>3445.46</v>
       </c>
     </row>
     <row r="590">
@@ -36445,7 +36445,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>2828.16</v>
+        <v>2871.22</v>
       </c>
     </row>
     <row r="591">
@@ -36506,7 +36506,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>4525.06</v>
+        <v>4593.95</v>
       </c>
     </row>
     <row r="592">
@@ -36567,7 +36567,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>18100.25</v>
+        <v>18375.81</v>
       </c>
     </row>
     <row r="593">
@@ -36628,7 +36628,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>3393.8</v>
+        <v>3445.46</v>
       </c>
     </row>
     <row r="594">
@@ -36689,7 +36689,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>4525.06</v>
+        <v>4593.95</v>
       </c>
     </row>
     <row r="595">
@@ -36750,7 +36750,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>7918.86</v>
+        <v>8039.42</v>
       </c>
     </row>
     <row r="596">
@@ -36811,7 +36811,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>4525.06</v>
+        <v>4593.95</v>
       </c>
     </row>
     <row r="597">
@@ -36872,7 +36872,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>2375.66</v>
+        <v>2411.82</v>
       </c>
     </row>
     <row r="598">
@@ -36933,7 +36933,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>7428.17</v>
+        <v>7541.26</v>
       </c>
     </row>
     <row r="599">
@@ -36994,7 +36994,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>6787.59</v>
+        <v>6890.93</v>
       </c>
     </row>
     <row r="600">
@@ -37055,7 +37055,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>5656.33</v>
+        <v>5742.44</v>
       </c>
     </row>
     <row r="601">
@@ -37116,7 +37116,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>3393.8</v>
+        <v>3476.33</v>
       </c>
     </row>
     <row r="602">
@@ -37177,7 +37177,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>22625.31</v>
+        <v>23175.51</v>
       </c>
     </row>
     <row r="603">
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>2367.21</v>
+        <v>2424.77</v>
       </c>
     </row>
     <row r="604">
@@ -37299,7 +37299,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>6787.59</v>
+        <v>6952.65</v>
       </c>
     </row>
     <row r="605">
@@ -37360,7 +37360,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>3393.8</v>
+        <v>3476.33</v>
       </c>
     </row>
     <row r="606">
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>4810.71</v>
+        <v>4927.69</v>
       </c>
     </row>
     <row r="607">
@@ -37482,7 +37482,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>5939.14</v>
+        <v>6083.57</v>
       </c>
     </row>
     <row r="608">
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>7483.32</v>
+        <v>7665.3</v>
       </c>
     </row>
     <row r="609">
@@ -37604,7 +37604,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9270.200000000001</v>
       </c>
     </row>
     <row r="610">
@@ -37665,7 +37665,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>2409.6</v>
+        <v>2468.19</v>
       </c>
     </row>
     <row r="611">
@@ -37726,7 +37726,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>11312.66</v>
+        <v>11587.75</v>
       </c>
     </row>
     <row r="612">
@@ -37787,7 +37787,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>4751.32</v>
+        <v>4866.86</v>
       </c>
     </row>
     <row r="613">
@@ -37848,7 +37848,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>4525.06</v>
+        <v>4635.1</v>
       </c>
     </row>
     <row r="614">
@@ -37909,7 +37909,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>5437.99</v>
+        <v>5570.23</v>
       </c>
     </row>
     <row r="615">
@@ -37970,7 +37970,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>5769.45</v>
+        <v>5909.75</v>
       </c>
     </row>
     <row r="616">
@@ -38031,7 +38031,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>3393.8</v>
+        <v>3476.33</v>
       </c>
     </row>
     <row r="617">
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>11312.66</v>
+        <v>11587.75</v>
       </c>
     </row>
     <row r="618">
@@ -38153,7 +38153,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>4525.06</v>
+        <v>4635.1</v>
       </c>
     </row>
     <row r="619">
@@ -38214,7 +38214,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>45250.62</v>
+        <v>46351.02</v>
       </c>
     </row>
     <row r="620">
@@ -38275,7 +38275,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>5656.33</v>
+        <v>5793.88</v>
       </c>
     </row>
     <row r="621">
@@ -38336,7 +38336,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>3393.8</v>
+        <v>3476.33</v>
       </c>
     </row>
     <row r="622">
@@ -38397,7 +38397,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>15837.72</v>
+        <v>16222.86</v>
       </c>
     </row>
     <row r="623">
@@ -38458,7 +38458,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>3393.8</v>
+        <v>3476.33</v>
       </c>
     </row>
     <row r="624">
@@ -38519,7 +38519,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>5656.33</v>
+        <v>5793.88</v>
       </c>
     </row>
     <row r="625">
@@ -38580,7 +38580,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>5656.33</v>
+        <v>5793.88</v>
       </c>
     </row>
     <row r="626">
@@ -38641,7 +38641,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>6221.96</v>
+        <v>6373.26</v>
       </c>
     </row>
     <row r="627">
@@ -38702,7 +38702,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>4468.5</v>
+        <v>4577.16</v>
       </c>
     </row>
     <row r="628">
@@ -38763,7 +38763,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>3266.79</v>
+        <v>3346.23</v>
       </c>
     </row>
     <row r="629">
@@ -38824,7 +38824,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>5656.33</v>
+        <v>5793.88</v>
       </c>
     </row>
     <row r="630">
@@ -38885,7 +38885,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>40386.18</v>
+        <v>41368.28</v>
       </c>
     </row>
     <row r="631">
@@ -38946,7 +38946,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>33937.97</v>
+        <v>34763.26</v>
       </c>
     </row>
     <row r="632">
@@ -39007,7 +39007,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>5656.33</v>
+        <v>5793.88</v>
       </c>
     </row>
     <row r="633">
@@ -39068,7 +39068,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>2488.78</v>
+        <v>2549.31</v>
       </c>
     </row>
     <row r="634">
@@ -39129,7 +39129,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>20362.78</v>
+        <v>20857.96</v>
       </c>
     </row>
     <row r="635">
@@ -39190,7 +39190,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>2715.04</v>
+        <v>2781.06</v>
       </c>
     </row>
     <row r="636">
@@ -39251,7 +39251,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>38463.03</v>
+        <v>39398.36</v>
       </c>
     </row>
     <row r="637">
@@ -39312,7 +39312,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>2375.66</v>
+        <v>2433.43</v>
       </c>
     </row>
     <row r="638">
@@ -39373,7 +39373,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>5656.33</v>
+        <v>5793.88</v>
       </c>
     </row>
     <row r="639">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>38601.23</v>
+        <v>39539.92</v>
       </c>
     </row>
     <row r="640">
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>5656.33</v>
+        <v>5793.88</v>
       </c>
     </row>
     <row r="641">
@@ -39556,7 +39556,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>2828.16</v>
+        <v>2899.66</v>
       </c>
     </row>
     <row r="642">
@@ -39617,7 +39617,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>4638.19</v>
+        <v>4755.44</v>
       </c>
     </row>
     <row r="643">
@@ -39678,7 +39678,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>7692.61</v>
+        <v>7887.08</v>
       </c>
     </row>
     <row r="644">
@@ -39739,7 +39739,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>73532.25999999999</v>
+        <v>75391.16</v>
       </c>
     </row>
     <row r="645">
@@ -39800,7 +39800,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>2375.66</v>
+        <v>2435.71</v>
       </c>
     </row>
     <row r="646">
@@ -39861,7 +39861,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>3167.54</v>
+        <v>3247.62</v>
       </c>
     </row>
     <row r="647">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>2375.66</v>
+        <v>2435.71</v>
       </c>
     </row>
     <row r="648">
@@ -39983,7 +39983,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>9615.76</v>
+        <v>9858.84</v>
       </c>
     </row>
     <row r="649">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>5656.33</v>
+        <v>5799.32</v>
       </c>
     </row>
     <row r="650">
@@ -40105,7 +40105,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>25122.47</v>
+        <v>25757.57</v>
       </c>
     </row>
     <row r="651">
@@ -40166,7 +40166,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>7918.8</v>
+        <v>8118.98</v>
       </c>
     </row>
     <row r="652">
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>22625.31</v>
+        <v>23197.28</v>
       </c>
     </row>
     <row r="653">
@@ -40288,7 +40288,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>7918.86</v>
+        <v>8119.05</v>
       </c>
     </row>
     <row r="654">
@@ -40349,7 +40349,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>54300.75</v>
+        <v>55673.48</v>
       </c>
     </row>
     <row r="655">
@@ -40410,7 +40410,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>7013.85</v>
+        <v>7191.16</v>
       </c>
     </row>
     <row r="656">
@@ -40471,7 +40471,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>5656.33</v>
+        <v>5799.32</v>
       </c>
     </row>
     <row r="657">
@@ -40532,7 +40532,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>39594.3</v>
+        <v>40595.24</v>
       </c>
     </row>
     <row r="658">
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>5564.43</v>
+        <v>5705.1</v>
       </c>
     </row>
     <row r="659">
@@ -40654,7 +40654,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>2828.16</v>
+        <v>2899.66</v>
       </c>
     </row>
     <row r="660">
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>2375.66</v>
+        <v>2435.71</v>
       </c>
     </row>
     <row r="661">
@@ -40776,7 +40776,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>11312.66</v>
+        <v>11598.64</v>
       </c>
     </row>
     <row r="662">
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>6787.59</v>
+        <v>6959.18</v>
       </c>
     </row>
     <row r="663">
@@ -40898,7 +40898,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>8620.24</v>
+        <v>8838.16</v>
       </c>
     </row>
     <row r="664">
@@ -40959,7 +40959,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>5656.33</v>
+        <v>5799.32</v>
       </c>
     </row>
     <row r="665">
@@ -41020,7 +41020,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>2375.66</v>
+        <v>2435.71</v>
       </c>
     </row>
     <row r="666">
@@ -41081,7 +41081,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>13008.22</v>
+        <v>13337.07</v>
       </c>
     </row>
     <row r="667">
@@ -41142,7 +41142,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>8484.49</v>
+        <v>8698.98</v>
       </c>
     </row>
     <row r="668">
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>9884.719999999999</v>
+        <v>10134.6</v>
       </c>
     </row>
     <row r="669">
@@ -41264,7 +41264,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9278.91</v>
       </c>
     </row>
     <row r="670">
@@ -41325,7 +41325,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>7918.86</v>
+        <v>8119.05</v>
       </c>
     </row>
     <row r="671">
@@ -41386,7 +41386,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>11312.66</v>
+        <v>11598.64</v>
       </c>
     </row>
     <row r="672">
@@ -41447,7 +41447,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>6787.59</v>
+        <v>6959.18</v>
       </c>
     </row>
     <row r="673">
@@ -41508,7 +41508,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>28281.64</v>
+        <v>29139.23</v>
       </c>
     </row>
     <row r="674">
@@ -41569,7 +41569,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>3959.43</v>
+        <v>4079.49</v>
       </c>
     </row>
     <row r="675">
@@ -41630,7 +41630,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2367.21</v>
+        <v>2438.99</v>
       </c>
     </row>
     <row r="676">
@@ -41691,7 +41691,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>33937.97</v>
+        <v>34967.07</v>
       </c>
     </row>
     <row r="677">
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>14706.45</v>
+        <v>15152.4</v>
       </c>
     </row>
     <row r="678">
@@ -41813,7 +41813,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>39028.66</v>
+        <v>40212.13</v>
       </c>
     </row>
     <row r="679">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>38463.03</v>
+        <v>39629.35</v>
       </c>
     </row>
     <row r="680">
@@ -41935,7 +41935,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9324.549999999999</v>
       </c>
     </row>
     <row r="681">
@@ -41996,7 +41996,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>22625.31</v>
+        <v>23311.38</v>
       </c>
     </row>
     <row r="682">
@@ -42057,7 +42057,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>31166.37</v>
+        <v>32111.43</v>
       </c>
     </row>
     <row r="683">
@@ -42118,7 +42118,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>4751.32</v>
+        <v>4895.39</v>
       </c>
     </row>
     <row r="684">
@@ -42179,7 +42179,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>7918.86</v>
+        <v>8158.98</v>
       </c>
     </row>
     <row r="685">
@@ -42240,7 +42240,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>2375.66</v>
+        <v>2447.7</v>
       </c>
     </row>
     <row r="686">
@@ -42301,7 +42301,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>13575.19</v>
+        <v>13986.83</v>
       </c>
     </row>
     <row r="687">
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>5656.33</v>
+        <v>5827.85</v>
       </c>
     </row>
     <row r="688">
@@ -42423,7 +42423,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>7918.86</v>
+        <v>8158.98</v>
       </c>
     </row>
     <row r="689">
@@ -42484,7 +42484,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>18100.25</v>
+        <v>18649.11</v>
       </c>
     </row>
     <row r="690">
@@ -42545,7 +42545,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>2375.66</v>
+        <v>2447.7</v>
       </c>
     </row>
     <row r="691">
@@ -42606,7 +42606,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>2375.66</v>
+        <v>2447.7</v>
       </c>
     </row>
     <row r="692">
@@ -42667,7 +42667,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>16968.98</v>
+        <v>17483.54</v>
       </c>
     </row>
     <row r="693">
@@ -42728,7 +42728,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>73532.25999999999</v>
+        <v>75761.99000000001</v>
       </c>
     </row>
     <row r="694">
@@ -42789,7 +42789,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>5090.7</v>
+        <v>5245.06</v>
       </c>
     </row>
     <row r="695">
@@ -42850,7 +42850,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>17534.62</v>
+        <v>18066.32</v>
       </c>
     </row>
     <row r="696">
@@ -42911,7 +42911,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>2375.66</v>
+        <v>2447.7</v>
       </c>
     </row>
     <row r="697">
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>4525.06</v>
+        <v>4662.28</v>
       </c>
     </row>
     <row r="698">
@@ -43033,7 +43033,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>67875.94</v>
+        <v>69934.14999999999</v>
       </c>
     </row>
     <row r="699">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>11312.66</v>
+        <v>11655.69</v>
       </c>
     </row>
     <row r="700">
@@ -43155,7 +43155,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>4525.06</v>
+        <v>4662.28</v>
       </c>
     </row>
     <row r="701">
@@ -43216,7 +43216,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>6787.59</v>
+        <v>6993.41</v>
       </c>
     </row>
     <row r="702">
@@ -43277,7 +43277,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>2367.21</v>
+        <v>2438.99</v>
       </c>
     </row>
     <row r="703">
@@ -43338,7 +43338,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>8484.49</v>
+        <v>8741.77</v>
       </c>
     </row>
     <row r="704">
@@ -43399,7 +43399,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>26584.74</v>
+        <v>27390.87</v>
       </c>
     </row>
     <row r="705">
@@ -43460,7 +43460,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>4525.06</v>
+        <v>4662.28</v>
       </c>
     </row>
     <row r="706">
@@ -43521,7 +43521,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>2375.66</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="707">
@@ -43582,7 +43582,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>9245.82</v>
+        <v>9520.629999999999</v>
       </c>
     </row>
     <row r="708">
@@ -43643,7 +43643,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>23756.58</v>
+        <v>24462.69</v>
       </c>
     </row>
     <row r="709">
@@ -43704,7 +43704,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>22625.31</v>
+        <v>23297.8</v>
       </c>
     </row>
     <row r="710">
@@ -43765,7 +43765,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>3393.8</v>
+        <v>3494.67</v>
       </c>
     </row>
     <row r="711">
@@ -43826,7 +43826,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9319.120000000001</v>
       </c>
     </row>
     <row r="712">
@@ -43887,7 +43887,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>3393.8</v>
+        <v>3494.67</v>
       </c>
     </row>
     <row r="713">
@@ -43948,7 +43948,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>2375.66</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="714">
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>2375.66</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="715">
@@ -44070,7 +44070,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>5656.33</v>
+        <v>5824.45</v>
       </c>
     </row>
     <row r="716">
@@ -44131,7 +44131,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>6164.28</v>
+        <v>6347.5</v>
       </c>
     </row>
     <row r="717">
@@ -44196,7 +44196,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>1149129.35</v>
+        <v>1183284.91</v>
       </c>
     </row>
     <row r="718">
@@ -44257,7 +44257,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>6117.17</v>
+        <v>6298.99</v>
       </c>
     </row>
     <row r="719">
@@ -44318,7 +44318,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>3393.8</v>
+        <v>3494.67</v>
       </c>
     </row>
     <row r="720">
@@ -44379,7 +44379,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>7918.86</v>
+        <v>8154.23</v>
       </c>
     </row>
     <row r="721">
@@ -44440,7 +44440,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>4525.06</v>
+        <v>4659.56</v>
       </c>
     </row>
     <row r="722">
@@ -44501,7 +44501,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>2375.66</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="723">
@@ -44562,7 +44562,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>5656.33</v>
+        <v>5824.45</v>
       </c>
     </row>
     <row r="724">
@@ -44623,7 +44623,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>2828.16</v>
+        <v>2912.23</v>
       </c>
     </row>
     <row r="725">
@@ -44684,7 +44684,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>4506.96</v>
+        <v>4640.92</v>
       </c>
     </row>
     <row r="726">
@@ -44745,7 +44745,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>15837.72</v>
+        <v>16308.46</v>
       </c>
     </row>
     <row r="727">
@@ -44806,7 +44806,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9319.120000000001</v>
       </c>
     </row>
     <row r="728">
@@ -44867,7 +44867,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>18665.88</v>
+        <v>19220.69</v>
       </c>
     </row>
     <row r="729">
@@ -44928,7 +44928,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>2375.66</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="730">
@@ -44989,7 +44989,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>7918.86</v>
+        <v>8154.23</v>
       </c>
     </row>
     <row r="731">
@@ -45050,7 +45050,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>2370</v>
+        <v>2440.44</v>
       </c>
     </row>
     <row r="732">
@@ -45111,7 +45111,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>7692.61</v>
+        <v>7921.25</v>
       </c>
     </row>
     <row r="733">
@@ -45172,7 +45172,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>2941.29</v>
+        <v>3028.71</v>
       </c>
     </row>
     <row r="734">
@@ -45233,7 +45233,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>2375.66</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="735">
@@ -45298,7 +45298,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>101813.91</v>
+        <v>104840.12</v>
       </c>
     </row>
     <row r="736">
@@ -45359,7 +45359,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>2828.16</v>
+        <v>2912.23</v>
       </c>
     </row>
     <row r="737">
@@ -45420,7 +45420,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>3280.67</v>
+        <v>3378.18</v>
       </c>
     </row>
     <row r="738">
@@ -45481,7 +45481,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>33937.97</v>
+        <v>34946.71</v>
       </c>
     </row>
     <row r="739">
@@ -45542,7 +45542,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>12813.85</v>
+        <v>13194.71</v>
       </c>
     </row>
     <row r="740">
@@ -45603,7 +45603,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>6787.59</v>
+        <v>6989.34</v>
       </c>
     </row>
     <row r="741">
@@ -45664,7 +45664,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>7918.86</v>
+        <v>8154.23</v>
       </c>
     </row>
     <row r="742">
@@ -45725,7 +45725,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>9050.120000000001</v>
+        <v>9319.120000000001</v>
       </c>
     </row>
     <row r="743">
@@ -45786,7 +45786,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>3393.8</v>
+        <v>3494.67</v>
       </c>
     </row>
     <row r="744">
@@ -45847,7 +45847,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>15837.72</v>
+        <v>16308.46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/suministro-de-combustibles/ene-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26909,7 +26909,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26970,7 +26970,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27458,7 +27458,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29593,7 +29593,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29715,7 +29715,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30081,7 +30081,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -31179,7 +31179,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31301,7 +31301,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31423,7 +31423,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31484,7 +31484,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31606,7 +31606,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31911,7 +31911,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32826,7 +32826,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32948,7 +32948,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -34290,7 +34290,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34351,7 +34351,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34839,7 +34839,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35083,7 +35083,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35144,7 +35144,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35388,7 +35388,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -37035,7 +37035,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37340,7 +37340,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38987,7 +38987,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39170,7 +39170,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39414,7 +39414,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39475,7 +39475,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39597,7 +39597,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -40024,7 +40024,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40634,7 +40634,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41122,7 +41122,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41183,7 +41183,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41244,7 +41244,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -42159,7 +42159,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -44187,7 +44187,7 @@
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L717" t="inlineStr">
@@ -44481,7 +44481,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44542,7 +44542,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -44725,7 +44725,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -44969,7 +44969,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45030,7 +45030,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45213,7 +45213,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45289,7 +45289,7 @@
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L735" t="inlineStr">
@@ -45461,7 +45461,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45644,7 +45644,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45705,7 +45705,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/ene-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/ene-2026.xlsx
@@ -9114,7 +9114,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -13469,7 +13469,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -35374,7 +35374,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
@@ -40444,7 +40444,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
@@ -44734,7 +44734,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
